--- a/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:56:24+00:00</t>
+    <t>2026-09-21T13:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T13:38:34+00:00</t>
+    <t>2026-09-22T07:55:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T07:55:38+00:00</t>
+    <t>2026-09-22T08:01:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T08:01:04+00:00</t>
+    <t>2026-09-22T08:07:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T08:07:02+00:00</t>
+    <t>2026-09-22T09:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T09:47:29+00:00</t>
+    <t>2026-09-22T12:54:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
+++ b/structureIG/ig/StructureDefinition-fr-bundle-document-ips.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T12:54:22+00:00</t>
+    <t>2026-09-22T12:56:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
